--- a/data/trans_dic/IQ26A_R2-Estudios-trans_dic.xlsx
+++ b/data/trans_dic/IQ26A_R2-Estudios-trans_dic.xlsx
@@ -533,7 +533,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -541,7 +541,7 @@
       <c r="F1" s="3" t="n"/>
       <c r="G1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="H1" s="3" t="n"/>
@@ -649,42 +649,42 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>14,67%</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>10,24%</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>13,48%</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
           <t>17,55%</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>11,03%</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="I4" s="2" t="inlineStr">
         <is>
           <t>14,76%</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>19,08%</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>14,67%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>10,24%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>13,48%</t>
-        </is>
-      </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>21,89%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>8,69%</t>
+          <t>8,54%</t>
         </is>
       </c>
     </row>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>11,3; 24,96</t>
+          <t>9,22; 22,59</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>6,27; 16,92</t>
+          <t>5,89; 16,98</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>7,85; 24,78</t>
+          <t>7,86; 21,61</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,76; 43,46</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>9,22; 21,31</t>
+          <t>12,35; 25,19</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>5,7; 16,87</t>
+          <t>6,44; 17,28</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>7,61; 22,46</t>
+          <t>8,45; 24,82</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>4,88; 46,71</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>12,07; 21,1</t>
+          <t>12,15; 20,87</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>7,14; 14,67</t>
+          <t>7,33; 15,2</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>9,45; 20,5</t>
+          <t>9,68; 19,85</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>2,5; 22,13</t>
+          <t>1,95; 20,34</t>
         </is>
       </c>
     </row>
@@ -789,42 +789,42 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>11,34%</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>11,83%</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>14,07%</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>20,74%</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
           <t>12,28%</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="H6" s="2" t="inlineStr">
         <is>
           <t>9,85%</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="I6" s="2" t="inlineStr">
         <is>
           <t>14,41%</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>22,58%</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>11,34%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>11,83%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>14,07%</t>
-        </is>
-      </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>19,77%</t>
+          <t>20,92%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>20,89%</t>
+          <t>20,82%</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>9,66; 14,91</t>
+          <t>9,07; 13,72</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>7,64; 12,21</t>
+          <t>9,59; 14,53</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>12,01; 17,29</t>
+          <t>11,45; 16,69</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>15,61; 32,29</t>
+          <t>13,88; 28,03</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>9,06; 13,61</t>
+          <t>9,79; 15,21</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>9,31; 14,18</t>
+          <t>7,75; 12,64</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>11,66; 16,79</t>
+          <t>11,76; 17,18</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>13,46; 26,94</t>
+          <t>13,43; 29,36</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>10,12; 13,49</t>
+          <t>10,27; 13,49</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>9,27; 12,71</t>
+          <t>9,23; 12,73</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>12,5; 16,18</t>
+          <t>12,49; 16,21</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>16,3; 26,75</t>
+          <t>15,85; 25,85</t>
         </is>
       </c>
     </row>
@@ -929,42 +929,42 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>13,1%</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>9,35%</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>16,14%</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>18,09%</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
           <t>14,81%</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>11,98%</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="I8" s="2" t="inlineStr">
         <is>
           <t>14,95%</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>28,82%</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>13,1%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>9,35%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>16,14%</t>
-        </is>
-      </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>17,32%</t>
+          <t>29,07%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>22,97%</t>
+          <t>23,62%</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>10,84; 19,71</t>
+          <t>9,13; 17,63</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>8,19; 16,81</t>
+          <t>5,92; 13,83</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>11,09; 20,14</t>
+          <t>11,94; 21,14</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>19,28; 39,59</t>
+          <t>10,28; 29,58</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>9,34; 18,09</t>
+          <t>10,91; 19,84</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>5,79; 13,99</t>
+          <t>7,98; 16,36</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>11,68; 20,79</t>
+          <t>10,77; 20,07</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>9,4; 28,25</t>
+          <t>19,53; 41,04</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>11,02; 17,73</t>
+          <t>11,23; 17,64</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>8,23; 13,98</t>
+          <t>7,96; 13,68</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>12,69; 18,84</t>
+          <t>12,46; 18,89</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>16,64; 31,28</t>
+          <t>16,58; 31,84</t>
         </is>
       </c>
     </row>
@@ -1069,42 +1069,42 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>12,12%</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>11,08%</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>14,53%</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>18,7%</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
           <t>13,63%</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>10,5%</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="I10" s="2" t="inlineStr">
         <is>
           <t>14,57%</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>24,22%</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>12,12%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>11,08%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>14,53%</t>
-        </is>
-      </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>17,88%</t>
+          <t>23,55%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>20,58%</t>
+          <t>20,82%</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>11,38; 15,74</t>
+          <t>10,17; 14,15</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>8,63; 12,63</t>
+          <t>9,29; 13,1</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>12,6; 16,86</t>
+          <t>12,32; 16,66</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>18,56; 31,16</t>
+          <t>13,88; 23,87</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>10,22; 14,19</t>
+          <t>11,84; 15,87</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>9,2; 13,2</t>
+          <t>8,67; 12,55</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>12,47; 16,98</t>
+          <t>12,71; 16,97</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>13,39; 23,93</t>
+          <t>18,13; 30,7</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>11,46; 14,41</t>
+          <t>11,42; 14,34</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>9,47; 12,24</t>
+          <t>9,61; 12,22</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>13,05; 16,08</t>
+          <t>13,03; 16,25</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>17,0; 25,21</t>
+          <t>17,03; 25,11</t>
         </is>
       </c>
     </row>
@@ -1252,7 +1252,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -1260,7 +1260,7 @@
       <c r="F1" s="3" t="n"/>
       <c r="G1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="H1" s="3" t="n"/>
@@ -1368,42 +1368,42 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
           <t>24</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="I4" s="2" t="inlineStr">
         <is>
           <t>11</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
+      <c r="J4" s="2" t="inlineStr">
         <is>
           <t>4</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>19</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -1436,42 +1436,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>12460</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>8765</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>9249</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
           <t>15603</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="H5" s="2" t="inlineStr">
         <is>
           <t>9942</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
+      <c r="I5" s="2" t="inlineStr">
         <is>
           <t>8680</t>
         </is>
       </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>2029</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>12460</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>8765</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>9249</t>
-        </is>
-      </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1682</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -1491,7 +1491,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>2029</t>
+          <t>1682</t>
         </is>
       </c>
     </row>
@@ -1504,62 +1504,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>10047; 22196</t>
+          <t>7826; 19185</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>5648; 15245</t>
+          <t>5041; 14533</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>4615; 14575</t>
+          <t>5392; 14828</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>81; 4621</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>7830; 18095</t>
+          <t>10980; 22404</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>4876; 14431</t>
+          <t>5801; 15569</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>5221; 15412</t>
+          <t>4968; 14599</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>375; 3588</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>20983; 36686</t>
+          <t>21120; 36278</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>12536; 25774</t>
+          <t>12879; 26708</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>12046; 26120</t>
+          <t>12339; 25289</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>585; 5166</t>
+          <t>384; 4004</t>
         </is>
       </c>
     </row>
@@ -1576,42 +1576,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>81</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>81</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>96</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
           <t>75</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="H7" s="2" t="inlineStr">
         <is>
           <t>62</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="I7" s="2" t="inlineStr">
         <is>
           <t>99</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
+      <c r="J7" s="2" t="inlineStr">
         <is>
           <t>28</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>81</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>81</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>96</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>32</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
@@ -1644,42 +1644,42 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>53386</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>56122</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>68344</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>25493</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
           <t>49899</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>43136</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="I8" s="2" t="inlineStr">
         <is>
           <t>66877</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>19816</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>53386</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>56122</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>68344</t>
-        </is>
-      </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>26341</t>
+          <t>18139</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -1699,7 +1699,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>46156</t>
+          <t>43632</t>
         </is>
       </c>
     </row>
@@ -1712,62 +1712,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>39226; 60565</t>
+          <t>42704; 64589</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>33481; 53467</t>
+          <t>45481; 68944</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>55715; 80244</t>
+          <t>55627; 81099</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>13700; 28340</t>
+          <t>17054; 34445</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>42625; 64070</t>
+          <t>39781; 61800</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>44143; 67270</t>
+          <t>33958; 55361</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>56659; 81588</t>
+          <t>54587; 79728</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>17935; 35893</t>
+          <t>11643; 25457</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>88767; 118326</t>
+          <t>90070; 118320</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>84610; 115926</t>
+          <t>84179; 116148</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>118694; 153686</t>
+          <t>118608; 153941</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>36026; 59108</t>
+          <t>33215; 54180</t>
         </is>
       </c>
     </row>
@@ -1784,42 +1784,42 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>42</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
           <t>36</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>27</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="I10" s="2" t="inlineStr">
         <is>
           <t>38</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
+      <c r="J10" s="2" t="inlineStr">
         <is>
           <t>22</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>42</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>13</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1852,42 +1852,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>20280</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>15220</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>29403</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>7793</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
           <t>25216</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="H11" s="2" t="inlineStr">
         <is>
           <t>19192</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
+      <c r="I11" s="2" t="inlineStr">
         <is>
           <t>25250</t>
         </is>
       </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>12464</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>20280</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>15220</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>29403</t>
-        </is>
-      </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>7746</t>
+          <t>12691</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -1907,7 +1907,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>20210</t>
+          <t>20484</t>
         </is>
       </c>
     </row>
@@ -1920,62 +1920,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>18455; 33570</t>
+          <t>14138; 27294</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>13127; 26932</t>
+          <t>9635; 22517</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>18720; 34013</t>
+          <t>21753; 38525</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>8340; 17123</t>
+          <t>4429; 12743</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>14459; 28004</t>
+          <t>18584; 33790</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>9432; 22783</t>
+          <t>12783; 26211</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>21281; 37882</t>
+          <t>18194; 33894</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>4204; 12633</t>
+          <t>8525; 17917</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>35834; 57654</t>
+          <t>36505; 57332</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>26591; 45156</t>
+          <t>25714; 44194</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>44567; 66128</t>
+          <t>43738; 66309</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>14643; 27516</t>
+          <t>14381; 27619</t>
         </is>
       </c>
     </row>
@@ -1992,42 +1992,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>130</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>113</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>151</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>45</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
           <t>135</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="H13" s="2" t="inlineStr">
         <is>
           <t>104</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
+      <c r="I13" s="2" t="inlineStr">
         <is>
           <t>148</t>
         </is>
       </c>
-      <c r="F13" s="2" t="inlineStr">
+      <c r="J13" s="2" t="inlineStr">
         <is>
           <t>54</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>130</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>113</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>151</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>45</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
@@ -2060,42 +2060,42 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>86127</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>80108</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>106996</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>33286</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
           <t>90719</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="H14" s="2" t="inlineStr">
         <is>
           <t>72270</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="I14" s="2" t="inlineStr">
         <is>
           <t>100807</t>
         </is>
       </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>34308</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>86127</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>80108</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>106996</t>
-        </is>
-      </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>34087</t>
+          <t>32512</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2115,7 +2115,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>68395</t>
+          <t>65798</t>
         </is>
       </c>
     </row>
@@ -2128,62 +2128,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>75760; 104758</t>
+          <t>72231; 100546</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>59395; 86929</t>
+          <t>67118; 94708</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>87132; 116586</t>
+          <t>90733; 122750</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>26286; 44143</t>
+          <t>24706; 42485</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>72588; 100803</t>
+          <t>78806; 105613</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>66481; 95393</t>
+          <t>59649; 86380</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>91825; 125082</t>
+          <t>87884; 117410</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>25523; 45615</t>
+          <t>25021; 42385</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>157707; 198223</t>
+          <t>157190; 197258</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>133597; 172759</t>
+          <t>135631; 172370</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>186417; 229676</t>
+          <t>186116; 232128</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>56479; 83764</t>
+          <t>53818; 79361</t>
         </is>
       </c>
     </row>
